--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי אפללו – שיר של אהבה</v>
+        <v>ספיר סבן &amp; שלומי שבת - בליבי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a7%d7%95%d7%91%d7%99-%d7%90%d7%a4%d7%9c%d7%9c%d7%95-%d7%a9%d7%99%d7%a8-%d7%a9%d7%9c-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410257&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר יושב היטב בתוך העולם הסגנוני של קובי אפללו – בלדה רכה, רגשית, עם דגש על אינטימיות, זיכרון וזוגיות מתמשכת. השיר עוסק בכמה נושאים מרכזיים: אהבה מתמשכת לאורך שנים, התמודדות עם קשיים (“כשהכאב נגע…”), זיכרון ככוח מחזק, יצירה משותפת של</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי אפללו – שיר של אהבה</v>
+        <v>ספיר סבן &amp; שלומי שבת - בליבי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>נתי שקד - גשם</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410256&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>נתי שקד - גשם</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>לידור עמירה - חלום</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410255&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>לידור עמירה - חלום</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ישראל מועלמי - שמרתי קצת מרחק</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410254&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ישראל מועלמי - שמרתי קצת מרחק</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ישראל מועלמי - דור מלא נסיונות</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410253&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ישראל מועלמי - דור מלא נסיונות</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יונתן רזאל - היינו כחולמים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410252&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יונתן רזאל - היינו כחולמים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>בר סיידו - הימים שאחריך</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410251&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>בר סיידו - הימים שאחריך</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>נגה ארז Stuck In Heaven</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="C9" t="str">
+        <v>https://yosmusic.com/%d7%a0%d7%92%d7%94-%d7%90%d7%a8%d7%96-stuck-in-heaven/</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>Stuck In Heaven של נגה ארז הוא דוגמה  לפער בין סאונד פופ קצבי, כמעט “כיפי”, לבין תוכן רגשי מורכב ואפילו מטריד. זה בדיוק אחד הסימנים המסחריים של נגה ארז: מוזיקה שמרקידה אותך, בזמן שהמילים עושות לך קצת אי־נוחות. מבחינה מוזיקלית,</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>נגה ארז Stuck In Heaven</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ספיר סבן &amp; שלומי שבת - בליבי</v>
+        <v>שיר אמלי - אזמהניה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410257&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410260&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-29</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ספיר סבן &amp; שלומי שבת - בליבי</v>
+        <v>שיר אמלי - אזמהניה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתי שקד - גשם</v>
+        <v>רשל רובין - יש לי כוח</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410256&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410259&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-29</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתי שקד - גשם</v>
+        <v>רשל רובין - יש לי כוח</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>לידור עמירה - חלום</v>
+        <v>עברי לידר - ביונסה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410255&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410258&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-29</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>לידור עמירה - חלום</v>
+        <v>עברי לידר - ביונסה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ישראל מועלמי - שמרתי קצת מרחק</v>
+        <v>ספיר סבן שלומי שבת – בליבי</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-29</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410254&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
+        <v>https://yosmusic.com/%d7%a1%d7%a4%d7%99%d7%a8-%d7%a1%d7%91%d7%9f-%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%aa-%d7%91%d7%9c%d7%99%d7%91%d7%99/</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-29</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>השיר “בליבי” בדואט של ספיר סבן ושלומי שבת הוא מפגש בין נוסטלגיה טלוויזיונית, זהות מוזיקלית ים־תיכונית, ורב־לשוניות רגשית. עצם החיבור ביניהם – עשור אחרי The Voice ישראל – מוסיף רובד מטא־רגשי: לא רק כשיר על געגוע, אלא גם – סגירת</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,164 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ישראל מועלמי - שמרתי קצת מרחק</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ישראל מועלמי - דור מלא נסיונות</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410253&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ישראל מועלמי - דור מלא נסיונות</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יונתן רזאל - היינו כחולמים</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410252&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יונתן רזאל - היינו כחולמים</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>בר סיידו - הימים שאחריך</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410251&amp;sid=908f011ce84bbbc22de8cbb2f75a648f</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>בר סיידו - הימים שאחריך</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>נגה ארז Stuck In Heaven</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%92%d7%94-%d7%90%d7%a8%d7%96-stuck-in-heaven/</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>Stuck In Heaven של נגה ארז הוא דוגמה  לפער בין סאונד פופ קצבי, כמעט “כיפי”, לבין תוכן רגשי מורכב ואפילו מטריד. זה בדיוק אחד הסימנים המסחריים של נגה ארז: מוזיקה שמרקידה אותך, בזמן שהמילים עושות לך קצת אי־נוחות. מבחינה מוזיקלית,</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>נגה ארז Stuck In Heaven</v>
+        <v>ספיר סבן שלומי שבת – בליבי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר אמלי - אזמהניה</v>
+        <v>מינקובסקי – מכלוף</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410260&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a0%d7%a7%d7%95%d7%91%d7%a1%d7%a7%d7%99-%d7%9e%d7%9b%d7%9c%d7%95%d7%a3/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>“מינקובסקי” שכתב מינקובסקי בביצוע מכלוף – הוא טקסט מורכב הרבה יותר ממה שנראה במבט ראשון. יש כאן שילוב של ראפ, פופ, הומור עצמי, זהות עדתית ומטא־אמירה על הצלחה ואותנטיות. השיר נפתח בשאלה דיבורית: “מה אתה מנסה להגיד / שאתה?! אתה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר אמלי - אזמהניה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רשל רובין - יש לי כוח</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410259&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רשל רובין - יש לי כוח</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עברי לידר - ביונסה</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410258&amp;sid=8ccdaa6e1ca5bee9c9c53d156e54fbee</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עברי לידר - ביונסה</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ספיר סבן שלומי שבת – בליבי</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%a4%d7%99%d7%a8-%d7%a1%d7%91%d7%9f-%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%aa-%d7%91%d7%9c%d7%99%d7%91%d7%99/</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>השיר “בליבי” בדואט של ספיר סבן ושלומי שבת הוא מפגש בין נוסטלגיה טלוויזיונית, זהות מוזיקלית ים־תיכונית, ורב־לשוניות רגשית. עצם החיבור ביניהם – עשור אחרי The Voice ישראל – מוסיף רובד מטא־רגשי: לא רק כשיר על געגוע, אלא גם – סגירת</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>ספיר סבן שלומי שבת – בליבי</v>
+        <v>מינקובסקי – מכלוף</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מינקובסקי – מכלוף</v>
+        <v>הראל סקעת – אמונה שבורה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a0%d7%a7%d7%95%d7%91%d7%a1%d7%a7%d7%99-%d7%9e%d7%9b%d7%9c%d7%95%d7%a3/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%90%d7%9e%d7%95%d7%a0%d7%94-%d7%a9%d7%91%d7%95%d7%a8%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-30</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“מינקובסקי” שכתב מינקובסקי בביצוע מכלוף – הוא טקסט מורכב הרבה יותר ממה שנראה במבט ראשון. יש כאן שילוב של ראפ, פופ, הומור עצמי, זהות עדתית ומטא־אמירה על הצלחה ואותנטיות. השיר נפתח בשאלה דיבורית: “מה אתה מנסה להגיד / שאתה?! אתה</v>
+        <v>הראל סקעת שר בלדה שמצליחה לגעת בנושא עמוק – משבר אמונה דרך הגשה עדינה, כמעט מתפללת. כבר מהשורה – “באמונה שבורה באתי נקי עד אליך” נוצר מתח. מצד אחד: רצון להיות “נקי”, כן, פתוח. מצד שני: אמונה שנשברה- משהו בסיסי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מינקובסקי – מכלוף</v>
+        <v>הראל סקעת – אמונה שבורה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל סקעת – אמונה שבורה</v>
+        <v>שי וינר - יבוא שלום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%90%d7%9e%d7%95%d7%a0%d7%94-%d7%a9%d7%91%d7%95%d7%a8%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410287&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-30</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הראל סקעת שר בלדה שמצליחה לגעת בנושא עמוק – משבר אמונה דרך הגשה עדינה, כמעט מתפללת. כבר מהשורה – “באמונה שבורה באתי נקי עד אליך” נוצר מתח. מצד אחד: רצון להיות “נקי”, כן, פתוח. מצד שני: אמונה שנשברה- משהו בסיסי</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,962 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל סקעת – אמונה שבורה</v>
+        <v>שי וינר - יבוא שלום</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שחר גזנלי - 2 כוסות יין</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410286&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שחר גזנלי - 2 כוסות יין</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>קול החברים - מחרוזת רוקדת בלילות 2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410285&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>קול החברים - מחרוזת רוקדת בלילות 2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עמית סמוכי - ראויה לאהבה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410284&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עמית סמוכי - ראויה לאהבה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עופר בדיחי - בצל עצי התאנה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410283&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עופר בדיחי - בצל עצי התאנה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>סטפן לגר - מינימום</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410282&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>סטפן לגר - מינימום</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>נוי אביטל - ההצגה חייבת להימשך</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410281&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>נוי אביטל - ההצגה חייבת להימשך</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>מנשה סביליה - מחרוזת אם קצת עצוב 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410280&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>מנשה סביליה - מחרוזת אם קצת עצוב 2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>מינקובסקי - מכלוף</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410279&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>מינקובסקי - מכלוף</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>מאור אברהם - כל הלילה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410278&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>מאור אברהם - כל הלילה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>מאור אברהם - הלב הזה שלך</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410277&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>מאור אברהם - הלב הזה שלך</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>יוסף נטיב - אנשים כאלה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410276&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>יוסף נטיב - אנשים כאלה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>יוסי שטרית - חורף אחד בלעדייך</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410275&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>יוסי שטרית - חורף אחד בלעדייך</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>האחים אהרון - השם ישמרך</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410274&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>האחים אהרון - השם ישמרך</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>בני אלבז - עם פלדה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410273&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>בני אלבז - עם פלדה</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אריאל רביבו - גאולה</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410272&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אריאל רביבו - גאולה</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אריאל לוי - מחרוזת שמח בני 2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410271&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אריאל לוי - מחרוזת שמח בני 2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>תמר אופיר - בדמייך חיי</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410270&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>תמר אופיר - בדמייך חיי</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>ליאל נחתום - שערי שמים פתח</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410269&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>ליאל נחתום - שערי שמים פתח</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>הראל סקעת - אמונה שבורה</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410268&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>הראל סקעת - אמונה שבורה</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>החצר האחורית של ג'וני - לבד</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410267&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>החצר האחורית של ג'וני - לבד</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>הודיה בנישו - בינתיים</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C23" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410266&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>הודיה בנישו - בינתיים</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>אליהו חייט - אני קורא לך</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C24" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410265&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>אליהו חייט - אני קורא לך</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>אור סלמן - הלב הטוב ינצח</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C25" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410264&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>אור סלמן - הלב הטוב ינצח</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>אהרון ירימי &amp; ששי יעיש - אביר ישראל 2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C26" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410263&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>אהרון ירימי &amp; ששי יעיש - אביר ישראל 2026</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>אביר יעקב - עד מתי נעצור</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="C27" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410262&amp;sid=3612540fa415c96bdef2bc80ef164ed7</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>אביר יעקב - עד מתי נעצור</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L27"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>החצר האחורית של ג'וני לבד</v>
+        <v>החצר האחורית של ג'וני – לבד</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>החצר האחורית של ג'וני לבד</v>
+        <v>החצר האחורית של ג'וני – לבד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>החצר האחורית של ג'וני – לבד</v>
+        <v>אהרן רזאל &amp; הרב שלמה כ"ץ - ועשו לי מקדש</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%97%d7%a6%d7%a8-%d7%94%d7%90%d7%97%d7%95%d7%a8%d7%99%d7%aa-%d7%a9%d7%9c-%d7%92%d7%95%d7%a0%d7%99-%d7%9c%d7%91%d7%93/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410290&amp;sid=7985c882a7deca566a6f288096b142ba</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-31</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר לבד של יונתן כהן (מהפרויקט “החצר האחורית של ג’וני”) הוא שיר חשוף, כמעט כמו מונולוג אישי—שנע בין סיפור חיים, וידוי נפשי וביקורת חברתית, עטוף בסאונד ים־תיכוני עם נגיעות היפ־הופ. השורה: “עברתי את מסע החיים הרבה לפני משבר 40” היא</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>החצר האחורית של ג'וני – לבד</v>
+        <v>אהרן רזאל &amp; הרב שלמה כ"ץ - ועשו לי מקדש</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אדרת - ושמחת בחגך</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410289&amp;sid=7985c882a7deca566a6f288096b142ba</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אדרת - ושמחת בחגך</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אברהם אביב אלוש - אז ישיר (שבת מכל הסיבות)</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410288&amp;sid=7985c882a7deca566a6f288096b142ba</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אברהם אביב אלוש - אז ישיר (שבת מכל הסיבות)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אהרן רזאל &amp; הרב שלמה כ"ץ - ועשו לי מקדש</v>
+        <v>ישראל ורולקר - אנא אל חי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410290&amp;sid=7985c882a7deca566a6f288096b142ba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410298&amp;sid=cd57821f7a473b351f987152c916e91c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-31</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אהרן רזאל &amp; הרב שלמה כ"ץ - ועשו לי מקדש</v>
+        <v>ישראל ורולקר - אנא אל חי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אדרת - ושמחת בחגך</v>
+        <v>ישי ריבו - לא לחינם</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410289&amp;sid=7985c882a7deca566a6f288096b142ba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410297&amp;sid=cd57821f7a473b351f987152c916e91c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-31</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אדרת - ושמחת בחגך</v>
+        <v>ישי ריבו - לא לחינם</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אברהם אביב אלוש - אז ישיר (שבת מכל הסיבות)</v>
+        <v>יניב חיו &amp; שמואל דנה - חיזרי אליי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410288&amp;sid=7985c882a7deca566a6f288096b142ba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410296&amp;sid=cd57821f7a473b351f987152c916e91c</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-31</v>
@@ -545,12 +545,202 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אברהם אביב אלוש - אז ישיר (שבת מכל הסיבות)</v>
+        <v>יניב חיו &amp; שמואל דנה - חיזרי אליי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>יוחאי אביטן - בן טוב</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410295&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>יוחאי אביטן - בן טוב</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>גיא זו-ארץ &amp; רועי זו-ארץ - והיא שעמדה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410294&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>גיא זו-ארץ &amp; רועי זו-ארץ - והיא שעמדה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>בנצ'ו - מודה לבורא</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410293&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>בנצ'ו - מודה לבורא</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>איתי בירמן &amp; בן ארצי - נלחמתי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410292&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>איתי בירמן &amp; בן ארצי - נלחמתי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אילן חדד - מחרוזת חפלה 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410291&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אילן חדד - מחרוזת חפלה 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ישראל ורולקר - אנא אל חי</v>
+        <v>צח חכים - זמן אחר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410298&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410302&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-31</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ישראל ורולקר - אנא אל חי</v>
+        <v>צח חכים - זמן אחר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ישי ריבו - לא לחינם</v>
+        <v>נתי לוי לב - רמי לוי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410297&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410301&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-31</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ישי ריבו - לא לחינם</v>
+        <v>נתי לוי לב - רמי לוי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יניב חיו &amp; שמואל דנה - חיזרי אליי</v>
+        <v>מוריה מעטוף - בואי לאהוב איתי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410296&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410300&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-31</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יניב חיו &amp; שמואל דנה - חיזרי אליי</v>
+        <v>מוריה מעטוף - בואי לאהוב איתי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יוחאי אביטן - בן טוב</v>
+        <v>מור דהרי &amp; אריאל קנדאבי &amp; ארין קנדאבי &amp; אסף פפל - שמע ישראל</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410295&amp;sid=cd57821f7a473b351f987152c916e91c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410299&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-31</v>
@@ -583,164 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יוחאי אביטן - בן טוב</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>גיא זו-ארץ &amp; רועי זו-ארץ - והיא שעמדה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410294&amp;sid=cd57821f7a473b351f987152c916e91c</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>גיא זו-ארץ &amp; רועי זו-ארץ - והיא שעמדה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>בנצ'ו - מודה לבורא</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410293&amp;sid=cd57821f7a473b351f987152c916e91c</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>בנצ'ו - מודה לבורא</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>איתי בירמן &amp; בן ארצי - נלחמתי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410292&amp;sid=cd57821f7a473b351f987152c916e91c</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>איתי בירמן &amp; בן ארצי - נלחמתי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אילן חדד - מחרוזת חפלה 2026</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410291&amp;sid=cd57821f7a473b351f987152c916e91c</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אילן חדד - מחרוזת חפלה 2026</v>
+        <v>מור דהרי &amp; אריאל קנדאבי &amp; ארין קנדאבי &amp; אסף פפל - שמע ישראל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צח חכים - זמן אחר</v>
+        <v>נותי פוקס &amp; משולם זושא - קרב יום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410302&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410307&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-31</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צח חכים - זמן אחר</v>
+        <v>נותי פוקס &amp; משולם זושא - קרב יום</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתי לוי לב - רמי לוי</v>
+        <v>יוסי אזולאי מארח אמנים - אני מאמין</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410301&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410306&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-31</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתי לוי לב - רמי לוי</v>
+        <v>יוסי אזולאי מארח אמנים - אני מאמין</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מוריה מעטוף - בואי לאהוב איתי</v>
+        <v>זהבה כהן - Azadi</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410300&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410305&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-31</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מוריה מעטוף - בואי לאהוב איתי</v>
+        <v>זהבה כהן - Azadi</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מור דהרי &amp; אריאל קנדאבי &amp; ארין קנדאבי &amp; אסף פפל - שמע ישראל</v>
+        <v>דייויד טויב &amp; מוישלה שניידר &amp; גיל ישראלוב - חד גדיא</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410299&amp;sid=ea2a0111dc4ccedde01bcf1ee21aae4a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410304&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-31</v>
@@ -583,12 +583,50 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מור דהרי &amp; אריאל קנדאבי &amp; ארין קנדאבי &amp; אסף פפל - שמע ישראל</v>
+        <v>דייויד טויב &amp; מוישלה שניידר &amp; גיל ישראלוב - חד גדיא</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>איתמר ועקנין - בֶּאֱמוּנָה שְׁלֵמָה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410303&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>איתמר ועקנין - בֶּאֱמוּנָה שְׁלֵמָה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נותי פוקס &amp; משולם זושא - קרב יום</v>
+        <v>עידן צ'או - תשע נשמות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410307&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410312&amp;sid=dbb2bf83c53fa21d8f400788b6d36c15</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-31</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נותי פוקס &amp; משולם זושא - קרב יום</v>
+        <v>עידן צ'או - תשע נשמות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יוסי אזולאי מארח אמנים - אני מאמין</v>
+        <v>עומר קורן מארח את קובארי - שום דבר לא יכול לקרות</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410306&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410311&amp;sid=dbb2bf83c53fa21d8f400788b6d36c15</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-31</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יוסי אזולאי מארח אמנים - אני מאמין</v>
+        <v>עומר קורן מארח את קובארי - שום דבר לא יכול לקרות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>זהבה כהן - Azadi</v>
+        <v>מוקולי - מציאות מסוכנת</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410305&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410310&amp;sid=dbb2bf83c53fa21d8f400788b6d36c15</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-31</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>זהבה כהן - Azadi</v>
+        <v>מוקולי - מציאות מסוכנת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>דייויד טויב &amp; מוישלה שניידר &amp; גיל ישראלוב - חד גדיא</v>
+        <v>מועדון הקצב של אביהו פנחסוב - לא מפחד לרקוד</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410304&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410309&amp;sid=dbb2bf83c53fa21d8f400788b6d36c15</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-31</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>דייויד טויב &amp; מוישלה שניידר &amp; גיל ישראלוב - חד גדיא</v>
+        <v>מועדון הקצב של אביהו פנחסוב - לא מפחד לרקוד</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>איתמר ועקנין - בֶּאֱמוּנָה שְׁלֵמָה</v>
+        <v>טוני ג'ינו עם קלארק רוזנברג &amp; ג'אמבר - מסתכלת עליי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-31</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410303&amp;sid=c9a719ad1c178db44adff94ae00d1fc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410308&amp;sid=dbb2bf83c53fa21d8f400788b6d36c15</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-31</v>
@@ -621,7 +621,7 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>איתמר ועקנין - בֶּאֱמוּנָה שְׁלֵמָה</v>
+        <v>טוני ג'ינו עם קלארק רוזנברג &amp; ג'אמבר - מסתכלת עליי</v>
       </c>
     </row>
   </sheetData>
